--- a/outputs/evaluation/decision/CF_M05_decision_eval.xlsx
+++ b/outputs/evaluation/decision/CF_M05_decision_eval.xlsx
@@ -460,19 +460,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.125</v>
+        <v>0.4444</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0833</v>
+        <v>0.3636</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8403</v>
+        <v>0.8791</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8956</v>
+        <v>0.8668</v>
       </c>
       <c r="F2" t="n">
-        <v>0.785</v>
+        <v>0.8915</v>
       </c>
     </row>
     <row r="5">
@@ -499,10 +499,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7976</v>
+        <v>0.8786</v>
       </c>
     </row>
     <row r="7">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.125</v>
+        <v>0.4444</v>
       </c>
     </row>
     <row r="8">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0833</v>
+        <v>0.3636</v>
       </c>
     </row>
     <row r="9">
@@ -684,22 +684,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -709,22 +709,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -734,22 +734,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -763,7 +763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -831,57 +831,225 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>CF_M05_AD12</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.8391999999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.7812</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>C_06</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>AU_22</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>AWS is a consolidated cloud platform with robust services and a reliable infrastructure. [...] This diversity makes it easy to adapt to the needs of the project, allows growing and scaling the project in an agile way and eliminates the need to look for other platforms when requirements evolve.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>CF_M05_C06, CF_M05_C07</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>CF_M05_AU07</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>It allows you to automate the deployment, scaling and management of applications running in containers, run thousands of containers on different servers and ensure high availability.</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AD_03</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>CF_M05_AD3</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C3" t="n">
         <v>0.8956</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D3" t="n">
         <v>0.785</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>C_01</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>AU_09</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Això garanteix que la capa de presentació estigui disponible i actualitzada, facilitant el desplegament i reduint la dependència d’elements externs. D’aquesta manera, el portal no només centralitza l’accés, sinó que també assegura la coherència visual i funcional de tot l’ecosistema.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>This ensures that the presentation layer is available and updated [...] In this way, the portal not only centralizes access, but also ensures the visual and functional coherence of the entire ecosystem.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>CF_M05_C01 *</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>CF_M05_AU02</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>visual and functional coherence (the portal not only centralizes access, but also ensures the visual and functional coherence of the entire ecosystem.)</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="L3" t="n">
         <v>57</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AD_05</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CF_M05_AD6</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.8393</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>C_06</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>P_02</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>The use of this type of architecture allows high scalability, availability and accessibility [...] It also reduces maintainability, managed by the resource providers, and without large expenses, due to the fact that one pays for the resources consumed.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>CF_M05_C06, CF_M05_C07, CF_M05_C08 *</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>CF_M05_P05</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>scalability, availability, accessibility and maintainability (The use of this type of architecture allows high scalability, availability and accessibility, since resource management can be done according to needs and anywhere with an Internet connection. It also reduces maintainability, managed by resource providers, and without major expenses, since you pay for the resources consumed.)</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AD_01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CF_M05_AD1</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.8929</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>C_07</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>P_01</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Each microservice is deployed independently, which allows updates, scaling and maintenance without affecting the rest of the system. [...] This flexibility facilitates adaptation to change and the scalability of the application and improves the resilience of the system</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>CF_M05_C07 *</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>CF_M05_P01</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>flexibility and scalability (Each microservice is deployed independently, which allows updates, scaling and maintenance without affecting the rest of the system. It also allows each service to have its own programming language, database and environment. This flexibility facilitates adaptation to change and scalability of the application and improves the resilience of the system, since an error in a microservice does not mean the complete collapse of the application. )</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -895,7 +1063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -938,246 +1106,176 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_01</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>R_22</t>
+          <t>C_08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Aquesta estructura permet desenvolupar, desplegar i escalar cada servei de manera autònoma, facilitant el manteniment, la flexibilitat i l’evolució del sistema.</t>
+          <t>This microservice acts as a central point for traffic management and routing communications [...] it incorporates protection mechanisms to ensure the integrity and confidentiality of communications. Specifically, it blocks any unauthorized connection attempt</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CF_M05_AD1</t>
+          <t>CF_M05_AD6</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.6639</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>C_06</t>
+          <t>C_09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>L’ús d’aquest tipus d’arquitectura permet alta escalabilitat, disponibilitat i accessibilitat, ja que la gestió dels recursos es pot fer segons les necessitats i en qualsevol lloc amb connexió a Internet.</t>
+          <t>This microservice is essential to maintain the confidentiality and protection of data.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M05_AD6</t>
+          <t>CF_M05_AD8</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.7402</v>
+        <v>0.7553</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>R_07</t>
+          <t>C_02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>A més de la seva tasca d’encaminament, aquest component incorpora mecanismes de protecció per assegurar la integritat i la confidencialitat de les comunicacions. Concretament, bloqueja qualsevol intent de connexió no autoritzada i aplica determinats protocols de seguretat per prevenir accessos indeguts i possibles vulnerabilitats.</t>
+          <t>This separation of responsibilities allows the client to focus on presentation and user experience, while the server focuses on business logic, security, data integrity and persistence.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>61</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M05_AD2</t>
+          <t>CF_M05_AD8</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.7126</v>
+        <v>0.7238</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>R_08</t>
+          <t>C_04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Aquest microservei és essencial per mantenir la confidencialitat i protecció de dades.</t>
+          <t>Angular applies the MVVM pattern [...] The ViewModel acts as an intermediary between the View and the Model, providing the data that the view needs and managing user actions.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>62, 64</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CF_M05_AD6</t>
+          <t>CF_M05_AD1</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.5744</v>
+        <v>0.6442</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AD_06</t>
+          <t>AD_08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C_02</t>
+          <t>C_05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>P_05</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Angular aplica el patró MVVM (Model-View-ViewModel), ja que la seva arquitectura està basada en components i serveis. [...] El patró MVVM és un derivat del clàssic patró Model-Vista-Controlador, pensat per a la implementació d’interfícies d’usuari.</t>
+          <t>This structure clarifies roles, avoids unnecessary coupling and makes it easy to test, reuse and maintain the code over time.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CF_M05_AD12</t>
+          <t>CF_M05_AD6</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.6355</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>AD_07</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>C_05</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>AU_19</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Spring Boot organitza el codi seguint el patró a capes amb les quals se separen responsabilitats [...] Aquesta estructura clarifica rols, evita acoblaments innecessaris i facilita provar, reutilitzar i mantenir el codi amb el pas del temps.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>CF_M05_AD1</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>0.6232</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>AD_08</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>C_06</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AU_22</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Per això s’ha triat AWS en comptes d’altres opcions com Google Cloud Platform o Microsoft Azure. El fet de disposar de tants serveis disponibles deixa centrar l’esforç en el desenvolupament de la solució, sense haver d’invertir temps extra en qüestions d’infraestructura.</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>CF_M05_AD6</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>0.7383</v>
+        <v>0.6867</v>
       </c>
     </row>
   </sheetData>
@@ -1191,7 +1289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1234,73 +1332,73 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M05_AD1</t>
+          <t>CF_M05_AD2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M05_C07 *</t>
+          <t>CF_M05_C09 *</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CF_M05_P01</t>
+          <t>CF_M05_AU01</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>flexibility and scalability (Each microservice is deployed independently, which allows updates, scaling and maintenance without affecting the rest of the system. It also allows each service to have its own programming language, database and environment. This flexibility facilitates adaptation to change and scalability of the application and improves the resilience of the system, since an error in a microservice does not mean the complete collapse of the application. )</t>
+          <t>integrity and confidentiality (In addition to its routing task, this component incorporates protection mechanisms to ensure the integrity and confidentiality of communications.)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AD_01</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.729</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M05_AD2</t>
+          <t>CF_M05_AD4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M05_C09 *</t>
+          <t>*</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CF_M05_AU01</t>
+          <t>CF_M05_AU03</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>integrity and confidentiality (In addition to its routing task, this component incorporates protection mechanisms to ensure the integrity and confidentiality of communications.)</t>
+          <t>confidentiality (This microservice is essential for maintaining data confidentiality and protection.)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.7126</v>
+        <v>0.4219</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M05_AD4</t>
+          <t>CF_M05_AD5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1310,12 +1408,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CF_M05_AU03</t>
+          <t>CF_M05_AU04</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>confidentiality (This microservice is essential for maintaining data confidentiality and protection.)</t>
+          <t>This component acts as a traceability and audit mechanism, ensuring that each interaction is documented for later analysis, incident resolution and regulatory compliance.</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1323,17 +1421,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.4219</v>
+        <v>0.4072</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M05_AD5</t>
+          <t>CF_M05_AD7</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1343,293 +1441,123 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CF_M05_AU04</t>
+          <t>CF_M05_P02, CF_M05_AU06</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>This component acts as a traceability and audit mechanism, ensuring that each interaction is documented for later analysis, incident resolution and regulatory compliance.</t>
+          <t>presentation and user experience (This separation of responsibilities allows the client to focus on presentation and user experience.)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AD_01</t>
+          <t>AD_06</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.4072</v>
+        <v>0.4651</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M05_AD6</t>
+          <t>CF_M05_AD8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CF_M05_C06, CF_M05_C07, CF_M05_C08 *</t>
+          <t>CF_M05_C09 *</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CF_M05_P02</t>
+          <t>CF_M05_P02, CF_M05_AU32</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>scalability, availability, accessibility and maintainability (The use of this type of architecture allows high scalability, availability and accessibility, since resource management can be done according to needs and anywhere with an Internet connection. It also reduces maintainability, managed by resource providers, and without major expenses, since you pay for the resources consumed.)</t>
+          <t>security, data integrity, persistence (This separation of responsibilities allows [...] the server to focus on business logic, security, data integrity, and persistence.)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.7402</v>
+        <v>0.7553</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M05_AD7</t>
+          <t>CF_M05_AD9</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>CF_M05_C07 *</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CF_M05_P03, CF_M05_AU22</t>
+          <t>CF_M05_AU30</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>presentation and user experience (This separation of responsibilities allows the client to focus on presentation and user experience.)</t>
+          <t xml:space="preserve"> It allows you to create dynamic, interactive and scalable user interfaces, facilitating the development and maintenance of large applications.</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AD_06</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.317</v>
+        <v>0.7581</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M05_AD8</t>
+          <t>CF_M05_AD11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CF_M05_C09 *</t>
+          <t>*</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CF_M05_P03, CF_M05_AU23</t>
+          <t>CF_M05_AU30, CF_M05_AU29</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>security, data integrity, persistence (This separation of responsibilities allows [...] the server to focus on business logic, security, data integrity, and persistence.)</t>
+          <t>maintainability (When making the decision to use Angular for frontEnd development and Spring for the backEnd, several technological criteria were considered, the work methodology that would be implemented throughout the development of the application was thought about and the long-term maintainability of the project was taken into consideration.)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CF_M05_AD9</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>CF_M05_C07 *</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>CF_M05_AU17</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> It allows you to create dynamic, interactive and scalable user interfaces, facilitating the development and maintenance of large applications.</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>76</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>AD_02</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>0.6373</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CF_M05_AD10</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Spring Data &amp; JPA 2.2</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> This combination is used to manage data persistence, which allows you to interact with databases in a simpler, object-oriented way.</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>76</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>AD_07</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>0.3841</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CF_M05_AD11</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>CF_M05_AU17, CF_M05_AU18, CF_M05_AU19</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>maintainability (When making the decision to use Angular for frontEnd development and Spring for the backEnd, several technological criteria were considered, the work methodology that would be implemented throughout the development of the application was thought about and the long-term maintainability of the project was taken into consideration.)</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>77</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>AD_01</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>0.3323</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CF_M05_AD12</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>CF_M05_C06, CF_M05_C07</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>CF_M05_AU25</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>It allows you to automate the deployment, scaling and management of applications running in containers, run thousands of containers on different servers and ensure high availability.</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>81</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>AD_08</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>0.7364000000000001</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CF_M05_AD13</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>AD_01</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CF_M05_AD14</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>AD_01</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
+        <v>0.3405</v>
       </c>
     </row>
   </sheetData>
